--- a/artfynd/S 2213-2023 artfynd.xlsx
+++ b/artfynd/S 2213-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107241394</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111918736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418916</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418968</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418915</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418969</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103701982</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418917</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418970</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1708,6 +1758,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81809757</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81809787</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103701973</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418913</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103701975</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2226,6 +2301,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100969899</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2325,6 +2405,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100969900</t>
         </is>
       </c>
     </row>
@@ -2428,6 +2513,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113877444</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2550,6 +2640,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126762757</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2649,6 +2744,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100969897</t>
         </is>
       </c>
     </row>
@@ -2753,6 +2853,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113877441</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126762753</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3025,6 +3135,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57189185</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3124,6 +3239,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62231027</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3225,6 +3345,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100969901</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126762755</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3453,6 +3583,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100969891</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3554,6 +3689,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100969887</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3653,6 +3793,11 @@
       <c r="AY29" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100969896</t>
         </is>
       </c>
     </row>
@@ -3757,6 +3902,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113877443</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3888,6 +4038,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126762754</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3995,6 +4150,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73927733</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100969869</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4197,6 +4362,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418996</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4299,6 +4469,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418993</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4400,6 +4575,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418994</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4501,6 +4681,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418995</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4602,6 +4787,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418998</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4701,6 +4891,11 @@
       <c r="AY39" t="inlineStr">
         <is>
           <t>Kartläggning av Ängelholms kommun 2022</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103418988</t>
         </is>
       </c>
     </row>
@@ -4804,6 +4999,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96109046</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4905,6 +5105,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96109029</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5016,6 +5221,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80081553</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5126,8 +5336,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96109031</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>